--- a/notes_ccf_Semestre2_ProgrammationInformatique_Section01_G01.xlsx
+++ b/notes_ccf_Semestre2_ProgrammationInformatique_Section01_G01.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YOU-BER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YOU-BER\Desktop\M1 french\grades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E71E2D-1170-471B-8387-2E627D0E6F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E813214-E0E2-4071-A9E6-C19ADAA2E00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="119">
   <si>
     <t>Matricule</t>
   </si>
@@ -1473,7 +1473,7 @@
         <v>92</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>

--- a/notes_ccf_Semestre2_ProgrammationInformatique_Section01_G01.xlsx
+++ b/notes_ccf_Semestre2_ProgrammationInformatique_Section01_G01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YOU-BER\Desktop\M1 french\grades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E813214-E0E2-4071-A9E6-C19ADAA2E00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EACB7A6B-DE57-4438-AE62-D3E4FA4F5B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1346,7 +1346,7 @@
         <v>78</v>
       </c>
       <c r="D24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1525,7 +1525,7 @@
         <v>98</v>
       </c>
       <c r="D31">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -1551,7 +1551,7 @@
         <v>101</v>
       </c>
       <c r="D32">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
